--- a/data/gravel/Moots Routt CRD 2025.xlsx
+++ b/data/gravel/Moots Routt CRD 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4063726-6F30-2E42-8131-F211A129585B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5883BE0-4EFB-2B4C-BB2A-350B917A8638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25160" yWindow="-17580" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Stand Over (in)</t>
   </si>
   <si>
-    <t>https://moots.com/bikes/gravel/routt-45/</t>
-  </si>
-  <si>
     <t>a8:i32</t>
   </si>
   <si>
@@ -315,6 +312,15 @@
   </si>
   <si>
     <t>Routt CRD</t>
+  </si>
+  <si>
+    <t>https://moots.com/bikes/gravel/routt-crd/</t>
+  </si>
+  <si>
+    <t>https://moots.com/wp-content/uploads/2023/08/Routt_CRD_Trans_Am_01-copy.jpg.webp</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -674,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -698,7 +704,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -706,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1795,7 +1806,7 @@
         <v>51</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1803,7 +1814,7 @@
         <v>52</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Moots Routt CRD 2025.xlsx
+++ b/data/gravel/Moots Routt CRD 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5883BE0-4EFB-2B4C-BB2A-350B917A8638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116C612B-5751-304F-939E-1928DF57C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
   <si>
     <t>brand</t>
   </si>
@@ -272,9 +272,6 @@
     <t>rider_max_spec</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>drop bar</t>
   </si>
   <si>
@@ -321,6 +318,15 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, Colorado, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -661,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -680,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -704,12 +710,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -717,7 +723,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -725,7 +731,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:I8" si="0">K8</f>
@@ -782,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9:I11" si="1">K9*10</f>
@@ -839,7 +845,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -896,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -1067,7 +1073,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <f t="shared" ref="C14:I15" si="3">K14*10</f>
@@ -1124,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <f t="shared" si="3"/>
@@ -1181,7 +1187,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" ref="C16:I16" si="4">K16*25.4</f>
@@ -1655,7 +1661,7 @@
         <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1663,7 +1669,7 @@
         <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1671,7 +1677,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1806,7 +1812,7 @@
         <v>51</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1814,7 +1820,7 @@
         <v>52</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1901,7 +1907,15 @@
         <v>65</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Moots Routt CRD 2025.xlsx
+++ b/data/gravel/Moots Routt CRD 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116C612B-5751-304F-939E-1928DF57C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3CF635-C29A-5D43-9CE0-A5D7843CDAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -667,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1752,169 +1770,199 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69" s="1">
-        <v>5999</v>
+        <v>56</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>8250</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="1">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>95</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>96</v>
       </c>
     </row>

--- a/data/gravel/Moots Routt CRD 2025.xlsx
+++ b/data/gravel/Moots Routt CRD 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3CF635-C29A-5D43-9CE0-A5D7843CDAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EA165F-E015-0843-BDF8-BAB6C5BD30AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="520" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -314,9 +314,6 @@
     <t>https://moots.com/bikes/gravel/routt-crd/</t>
   </si>
   <si>
-    <t>https://moots.com/wp-content/uploads/2023/08/Routt_CRD_Trans_Am_01-copy.jpg.webp</t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>https://moots.com/cdn/shop/files/Routt_CRD_Trans_Am_01_copy.jpg?v=1762966699&amp;width=2200</t>
   </si>
 </sst>
 </file>
@@ -733,7 +733,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1770,32 +1770,32 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1868,7 +1868,7 @@
         <v>52</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1955,15 +1955,15 @@
         <v>65</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" t="s">
         <v>95</v>
-      </c>
-      <c r="B79" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
